--- a/output/pdf_financials_xlsx/SXTY.xlsx
+++ b/output/pdf_financials_xlsx/SXTY.xlsx
@@ -2327,13 +2327,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.436</v>
+        <v>0.288869</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.711395</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.325757</v>
       </c>
     </row>
     <row r="119">
@@ -3412,7 +3412,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>-0.147131</v>
       </c>

--- a/output/pdf_financials_xlsx/SXTY.xlsx
+++ b/output/pdf_financials_xlsx/SXTY.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.184468</v>
+        <v>-1.18448</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.31465</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.184468</v>
+        <v>-1.18448</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.31465</v>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.037247</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.035863</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.384061</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.037247</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.035863</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.384061</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.09511</v>
+        <v>0.057863</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.041761</v>
+        <v>0.005898</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.390348</v>
+        <v>0.006287</v>
       </c>
     </row>
     <row r="49">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -2871,7 +2871,11 @@
           <t>Reclamation deposit (Note 5)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.42754</v>
       </c>
@@ -4462,7 +4466,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">

--- a/output/pdf_financials_xlsx/SXTY.xlsx
+++ b/output/pdf_financials_xlsx/SXTY.xlsx
@@ -2055,13 +2055,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.002698</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.000576</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006132</v>
       </c>
     </row>
     <row r="102">
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.317666</v>
+        <v>0.320364</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.443433</v>
+        <v>0.444009</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.717823</v>
+        <v>0.711691</v>
       </c>
     </row>
     <row r="107">
@@ -3298,7 +3298,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
         <v>0.002698</v>
       </c>
